--- a/TSSI Model.xlsx
+++ b/TSSI Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF145DA-CBF0-4013-9933-0DE4065CB325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAF1594-6BFD-421E-9709-448E0EB66D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="1272" windowWidth="27216" windowHeight="16008" xr2:uid="{15DD2EF7-3D38-48BE-91C3-905AF47E584F}"/>
+    <workbookView xWindow="0" yWindow="4308" windowWidth="23040" windowHeight="9132" activeTab="1" xr2:uid="{15DD2EF7-3D38-48BE-91C3-905AF47E584F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
   <si>
     <t>Company Overview</t>
   </si>
@@ -328,25 +328,59 @@
   </si>
   <si>
     <t>DCF MC</t>
+  </si>
+  <si>
+    <t>EBITDA Guide</t>
+  </si>
+  <si>
+    <t>14.68M</t>
+  </si>
+  <si>
+    <t>3.97M</t>
+  </si>
+  <si>
+    <t>EPS Guide</t>
+  </si>
+  <si>
+    <t>226M</t>
+  </si>
+  <si>
+    <t>41.40M</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>TSSI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -417,7 +451,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +506,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -503,124 +549,132 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="37" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="37" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="37" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="7" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="37" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="7" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="39" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1036,909 +1090,909 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="H3" s="29" t="s">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="H3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="27" t="s">
         <v>4</v>
       </c>
       <c r="N3" s="1">
         <v>18.760000000000002</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="Q3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="29" t="s">
+      <c r="W3" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="59">
+      <c r="X3" s="51">
         <v>45966</v>
       </c>
-      <c r="Y3" s="59"/>
+      <c r="Y3" s="51"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-    </row>
-    <row r="6" spans="1:28" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+    </row>
+    <row r="6" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="H6" s="51" t="s">
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="H6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="O6" s="51" t="s">
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="O6" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="V6" s="51" t="s">
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="V6" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="39" t="s">
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="41"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="39"/>
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53" t="s">
+      <c r="C7" s="54"/>
+      <c r="D7" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="H7" s="52" t="s">
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="H7" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="60">
+      <c r="I7" s="54"/>
+      <c r="J7" s="52">
         <v>161</v>
       </c>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="O7" s="52" t="s">
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="O7" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="53">
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55">
         <v>28.4</v>
       </c>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
       <c r="V7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y7" s="40">
+      <c r="Y7" s="38">
         <f>D8</f>
         <v>17.88</v>
       </c>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="41"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="57">
+      <c r="C8" s="50"/>
+      <c r="D8" s="56">
         <v>17.88</v>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="H8" s="49" t="s">
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="H8" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="61">
+      <c r="I8" s="50"/>
+      <c r="J8" s="53">
         <v>2004</v>
       </c>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="O8" s="49" t="s">
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="O8" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="54">
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="58">
         <f>R7*D8</f>
         <v>507.79199999999997</v>
       </c>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="58"/>
       <c r="V8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y8" s="41">
+      <c r="Y8" s="39">
         <f>R7</f>
         <v>28.4</v>
       </c>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="41"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="57">
+      <c r="C9" s="50"/>
+      <c r="D9" s="56">
         <f>Q17/(Y8*1000)</f>
         <v>18.760837606153498</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="H9" s="49" t="s">
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="H9" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="61" t="s">
+      <c r="I9" s="50"/>
+      <c r="J9" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
-      <c r="O9" s="49" t="s">
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="O9" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="55">
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="59">
         <v>0</v>
       </c>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
+      <c r="S9" s="59"/>
+      <c r="T9" s="59"/>
       <c r="V9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Y9" s="41">
+      <c r="Y9" s="39">
         <f>-58.7-36.836+19.541+1.891+22.648</f>
         <v>-51.456000000000003</v>
       </c>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="58">
+      <c r="C10" s="50"/>
+      <c r="D10" s="57">
         <f>D9/D8-1</f>
         <v>4.9263848218875861E-2</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="H10" s="49" t="s">
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="H10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="J10" s="61" t="s">
+      <c r="I10" s="50"/>
+      <c r="J10" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="O10" s="49" t="s">
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="O10" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="54" t="s">
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
+      <c r="S10" s="58"/>
+      <c r="T10" s="58"/>
       <c r="V10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y10" s="41" t="s">
+      <c r="Y10" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="H11" s="49" t="s">
+      <c r="C11" s="50"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="H11" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="49"/>
-      <c r="J11" s="61" t="s">
+      <c r="I11" s="50"/>
+      <c r="J11" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="O11" s="49" t="s">
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="O11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="56">
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="60">
         <v>46022</v>
       </c>
-      <c r="S11" s="56"/>
-      <c r="T11" s="56"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
       <c r="V11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y11" s="41">
+      <c r="Y11" s="39">
         <f>R8+Y9</f>
         <v>456.33599999999996</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="37">
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="35">
         <v>2020</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="35">
         <v>2021</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="35">
         <v>2022</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="35">
         <v>2023</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="35">
         <v>2024</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="35">
         <v>2025</v>
       </c>
-      <c r="K13" s="45" t="s">
+      <c r="K13" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="45" t="s">
+      <c r="L13" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="M13" s="45" t="s">
+      <c r="M13" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="N13" s="45" t="s">
+      <c r="N13" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="Q13" s="64" t="s">
+      <c r="Q13" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="R13" s="64"/>
-      <c r="S13" s="46" t="s">
+      <c r="R13" s="49"/>
+      <c r="S13" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T13" s="64" t="s">
+      <c r="T13" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="U13" s="64"/>
+      <c r="U13" s="49"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="23">
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="21">
         <v>45062</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="21">
         <v>27410</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="21">
         <v>30637</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="21">
         <v>54399</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="21">
         <v>148144</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="21">
         <f>SUM(Model!N25:Q25)</f>
-        <v>332720</v>
-      </c>
-      <c r="K14" s="23">
+        <v>227457</v>
+      </c>
+      <c r="K14" s="21">
         <v>398000</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="21">
         <v>466000</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="21">
         <v>526000</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="21">
         <v>592000</v>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="21">
         <v>660000</v>
       </c>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="47">
+      <c r="P14" s="21"/>
+      <c r="Q14" s="45">
         <v>50000</v>
       </c>
-      <c r="R14" s="47">
+      <c r="R14" s="45">
         <v>16</v>
       </c>
-      <c r="S14" s="48">
+      <c r="S14" s="46">
         <v>0.12</v>
       </c>
-      <c r="T14" s="63" t="s">
+      <c r="T14" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="U14" s="63"/>
+      <c r="U14" s="48"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="23">
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="21">
         <v>129</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="21">
         <v>-295</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="21">
         <v>1297</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="21">
         <v>2070</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="21">
         <v>9111</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="21">
         <v>14372</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="21">
         <v>20300</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="21">
         <v>27300</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="21">
         <v>34200</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="21">
         <v>41800</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="21">
         <v>48800</v>
       </c>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="62">
+      <c r="P15" s="21"/>
+      <c r="Q15" s="47">
         <f>Q14*R14</f>
         <v>800000</v>
       </c>
-      <c r="R15" s="62"/>
-      <c r="T15" s="63" t="s">
+      <c r="R15" s="47"/>
+      <c r="T15" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="U15" s="63"/>
+      <c r="U15" s="48"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="23">
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="21">
         <v>79</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="21">
         <v>-1232</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="21">
         <v>-17</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="21">
         <v>134</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="21">
         <v>6134</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="21">
         <v>12445</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="21">
         <v>16400</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="21">
         <v>21200</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="21">
         <v>26300</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="21">
         <v>31800</v>
       </c>
-      <c r="O16" s="23">
+      <c r="O16" s="21">
         <v>36300</v>
       </c>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="62">
+      <c r="P16" s="21"/>
+      <c r="Q16" s="47">
         <f>Q15/(1+S14)^5</f>
         <v>453941.4845748794</v>
       </c>
-      <c r="R16" s="62"/>
-      <c r="T16" s="15" t="s">
+      <c r="R16" s="47"/>
+      <c r="T16" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="U16" s="15"/>
+      <c r="U16" s="13"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="34">
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="32">
         <f t="shared" ref="E17:L17" si="0">E16/E14</f>
         <v>1.7531401180595624E-3</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="32">
         <f t="shared" si="0"/>
         <v>-4.4947099598686611E-2</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="32">
         <f t="shared" si="0"/>
         <v>-5.5488461664001049E-4</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="32">
         <f t="shared" si="0"/>
         <v>2.46328057501057E-3</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="32">
         <f t="shared" si="0"/>
         <v>4.1405659358462035E-2</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="32">
         <f t="shared" si="0"/>
-        <v>3.7403823034383263E-2</v>
-      </c>
-      <c r="K17" s="34">
+        <v>5.4713638182161906E-2</v>
+      </c>
+      <c r="K17" s="32">
         <f t="shared" si="0"/>
         <v>4.1206030150753768E-2</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="32">
         <f t="shared" si="0"/>
         <v>4.5493562231759654E-2</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="32">
         <f t="shared" ref="M17:O17" si="1">M16/M14</f>
         <v>0.05</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="32">
         <f t="shared" si="1"/>
         <v>5.3716216216216216E-2</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="32">
         <f t="shared" si="1"/>
         <v>5.5E-2</v>
       </c>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="62">
+      <c r="P17" s="21"/>
+      <c r="Q17" s="47">
         <f>NPV(S14,K19:O19)+Q16</f>
         <v>532807.78801475931</v>
       </c>
-      <c r="R17" s="62"/>
-      <c r="T17" s="63" t="s">
+      <c r="R17" s="47"/>
+      <c r="T17" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="U17" s="63"/>
+      <c r="U17" s="48"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="23">
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="21">
         <v>-767</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="21">
         <v>-1232</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="21">
         <v>-17</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="21">
         <v>134</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="21">
         <v>6813</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="21">
         <v>9557</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="21">
         <v>13200</v>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="21">
         <v>17800</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="21">
         <v>23000</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="21">
         <v>28000</v>
       </c>
-      <c r="O19" s="23">
+      <c r="O19" s="21">
         <v>33000</v>
       </c>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="42">
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="40">
         <v>0</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="40">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="40">
         <v>0</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="40">
         <v>0</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="40">
         <v>0.24</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="40">
         <f>J16/(Y8*1000)</f>
         <v>0.43820422535211268</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="40">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L20" s="42">
+      <c r="L20" s="40">
         <v>0.74</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="40">
         <v>0.92</v>
       </c>
-      <c r="N20" s="42">
+      <c r="N20" s="40">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O20" s="42">
+      <c r="O20" s="40">
         <v>1.25</v>
       </c>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="42">
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="40">
         <v>0.46</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="40">
         <v>-0.56999999999999995</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="40">
         <v>0.71</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="40">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="40">
         <v>0.27</v>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="40">
         <f>J19/(Y8*1000)</f>
         <v>0.33651408450704223</v>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="40">
         <v>0.47</v>
       </c>
-      <c r="L21" s="42">
+      <c r="L21" s="40">
         <v>0.61</v>
       </c>
-      <c r="M21" s="42">
+      <c r="M21" s="40">
         <v>0.78</v>
       </c>
-      <c r="N21" s="42">
+      <c r="N21" s="40">
         <v>0.96</v>
       </c>
       <c r="O21" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="23">
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="21">
         <v>12674</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="21">
         <v>8187</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="21">
         <v>11421</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="21">
         <v>5834</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="21">
         <v>287856</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="21">
         <v>478605</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="21">
         <v>625000</v>
       </c>
-      <c r="L23" s="23">
+      <c r="L23" s="21">
         <v>775000</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="21">
         <v>970000</v>
       </c>
-      <c r="N23" s="23">
+      <c r="N23" s="21">
         <v>1180000</v>
       </c>
-      <c r="O23" s="23">
+      <c r="O23" s="21">
         <v>1370000</v>
       </c>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="43">
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41">
         <v>0.71</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="41">
         <v>0.45</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="41">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H24" s="43">
+      <c r="H24" s="41">
         <v>0.27</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="41">
         <v>11.86</v>
       </c>
-      <c r="J24" s="43">
+      <c r="J24" s="41">
         <v>16.61</v>
       </c>
-      <c r="K24" s="43">
+      <c r="K24" s="41">
         <v>21.7</v>
       </c>
-      <c r="L24" s="43">
+      <c r="L24" s="41">
         <v>26.9</v>
       </c>
-      <c r="M24" s="43">
+      <c r="M24" s="41">
         <v>33.6</v>
       </c>
-      <c r="N24" s="43">
+      <c r="N24" s="41">
         <v>40.799999999999997</v>
       </c>
-      <c r="O24" s="43">
+      <c r="O24" s="41">
         <v>47.4</v>
       </c>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="42">
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="40">
         <v>0.17</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="40">
         <v>0.23</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="40">
         <v>1.66</v>
       </c>
-      <c r="J26" s="42">
+      <c r="J26" s="40">
         <f>(Y11*1000)/J14</f>
-        <v>1.3715316181774464</v>
-      </c>
-      <c r="K26" s="23">
+        <v>2.0062517310964267</v>
+      </c>
+      <c r="K26" s="21">
         <v>1.32</v>
       </c>
-      <c r="L26" s="23">
+      <c r="L26" s="21">
         <v>1.27</v>
       </c>
-      <c r="M26" s="23">
+      <c r="M26" s="21">
         <v>1.25</v>
       </c>
-      <c r="N26" s="23">
+      <c r="N26" s="21">
         <v>1.22</v>
       </c>
-      <c r="O26" s="23">
+      <c r="O26" s="21">
         <v>1.2</v>
       </c>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="40">
         <v>57.52</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="42">
+      <c r="G27" s="40">
         <v>5.33</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="40">
         <v>26.92</v>
       </c>
-      <c r="J27" s="42">
+      <c r="J27" s="40">
         <v>33.81</v>
       </c>
       <c r="K27" s="1">
@@ -1959,22 +2013,31 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="D2:F4"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
@@ -1991,31 +2054,22 @@
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="D2:F4"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="T15:U15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2040,7 +2094,7 @@
     <col min="19" max="16384" width="11.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2054,16 +2108,16 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:20" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" s="63" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="63" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="63" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -2077,7 +2131,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>74</v>
       </c>
@@ -2120,8 +2174,18 @@
       <c r="Q5" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S5" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="T5" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="U5" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="V5"/>
+    </row>
+    <row r="6" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -2134,8 +2198,18 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-    </row>
-    <row r="7" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="U6" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6"/>
+    </row>
+    <row r="7" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>69</v>
       </c>
@@ -2175,218 +2249,255 @@
       <c r="O7" s="7">
         <v>33002</v>
       </c>
-      <c r="P7" s="8">
-        <v>102823</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>60746</v>
-      </c>
-      <c r="T7" s="10"/>
-    </row>
-    <row r="8" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="P7" s="7">
+        <v>31110</v>
+      </c>
+      <c r="Q7" s="64">
+        <v>30000</v>
+      </c>
+      <c r="S7" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="T7" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="U7" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="V7"/>
+    </row>
+    <row r="8" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11">
         <v>3775</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>3775</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="11">
         <f>14916-K8</f>
         <v>10715</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="11">
         <v>4201</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="11">
         <v>56766</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="11">
         <f>109697-L8-K8-J8</f>
         <v>38015</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="11">
         <f>113612-O8</f>
         <v>83149</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="11">
         <v>30463</v>
       </c>
-      <c r="P8" s="14">
-        <v>94900</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>56064</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="P8" s="11">
+        <v>28500</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>27500</v>
+      </c>
+      <c r="S8" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T8" s="68">
+        <v>0.01</v>
+      </c>
+      <c r="U8" s="69">
+        <v>0.12</v>
+      </c>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+    </row>
+    <row r="9" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11">
         <f t="shared" ref="H9:Q9" si="0">H7-H8</f>
         <v>1647</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <f t="shared" si="0"/>
         <v>1647</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="11">
         <f t="shared" si="0"/>
         <v>909</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="11">
         <f t="shared" si="0"/>
         <v>713</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="11">
         <f t="shared" si="0"/>
         <v>3718</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="11">
         <f t="shared" si="0"/>
         <v>2482</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="11">
         <f t="shared" si="0"/>
         <v>7028</v>
       </c>
-      <c r="O9" s="13">
+      <c r="O9" s="11">
         <f t="shared" si="0"/>
         <v>2539</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="11">
         <f t="shared" si="0"/>
-        <v>7923</v>
-      </c>
-      <c r="Q9" s="14">
+        <v>2610</v>
+      </c>
+      <c r="Q9" s="12">
         <f t="shared" si="0"/>
-        <v>4682</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="15" t="s">
+        <v>2500</v>
+      </c>
+      <c r="S9" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67">
+        <f>0.03+0.05+0.06+0.05</f>
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18">
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16">
         <f t="shared" ref="H10:Q10" si="1">H9/H7</f>
         <v>0.30376244928070822</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="16">
         <f t="shared" si="1"/>
         <v>0.30376244928070822</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="16">
         <f t="shared" si="1"/>
         <v>7.8200275292498275E-2</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="16">
         <f t="shared" si="1"/>
         <v>0.1450956450956451</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="16">
         <f t="shared" si="1"/>
         <v>6.1470802195621982E-2</v>
       </c>
-      <c r="M10" s="18">
+      <c r="M10" s="16">
         <f t="shared" si="1"/>
         <v>6.1288490505469542E-2</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="16">
         <f t="shared" si="1"/>
         <v>7.793561551171585E-2</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="16">
         <f t="shared" si="1"/>
         <v>7.6934731228410394E-2</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="16">
         <f t="shared" si="1"/>
-        <v>7.7054744561041791E-2</v>
-      </c>
-      <c r="Q10" s="19">
+        <v>8.3895853423336553E-2</v>
+      </c>
+      <c r="Q10" s="17">
         <f t="shared" si="1"/>
-        <v>7.7075033747077998E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="15" t="s">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="S10" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67">
+        <v>14.68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="18">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="16">
         <f t="shared" ref="J11:P11" si="2">J7/F7-1</f>
         <v>5.7346465816917727</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="16">
         <f t="shared" si="2"/>
         <v>-0.53610875106202216</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="16">
         <f t="shared" si="2"/>
         <v>10.15529324972335</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="16">
         <f t="shared" si="2"/>
         <v>6.4690151235706379</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="16">
         <f t="shared" si="2"/>
         <v>6.7578286304198212</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="16">
         <f t="shared" si="2"/>
         <v>5.7159137159137163</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="16">
         <f t="shared" si="2"/>
-        <v>0.70000330665961252</v>
-      </c>
-      <c r="Q11" s="19">
+        <v>-0.48564909728192585</v>
+      </c>
+      <c r="Q11" s="17">
         <f>Q7/M7-1</f>
-        <v>0.50001234659357485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+        <v>-0.25920438551003777</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
       <c r="S12" s="4"/>
     </row>
-    <row r="13" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
@@ -2426,213 +2537,213 @@
       <c r="O13" s="7">
         <v>1482</v>
       </c>
-      <c r="P13" s="8">
-        <v>2540</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="P13" s="7">
+        <v>1600</v>
+      </c>
+      <c r="Q13" s="64">
         <v>1944</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11">
         <v>773</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>773</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="11">
         <f>1543-K14</f>
         <v>945</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="11">
         <v>598</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="11">
         <v>1228</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="11">
         <f>3075-L14-K14-J14</f>
         <v>304</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="11">
         <f>1148-O14</f>
         <v>767</v>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="11">
         <v>381</v>
       </c>
-      <c r="P14" s="14">
-        <v>1092</v>
-      </c>
-      <c r="Q14" s="14">
+      <c r="P14" s="11">
+        <v>700</v>
+      </c>
+      <c r="Q14" s="12">
         <v>836</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
+    <row r="15" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11">
         <f t="shared" ref="H15:Q15" si="3">H13-H14</f>
         <v>1031</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="11">
         <f t="shared" si="3"/>
         <v>1031</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="11">
         <f t="shared" si="3"/>
         <v>1201</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="11">
         <f t="shared" si="3"/>
         <v>1687</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="11">
         <f t="shared" si="3"/>
         <v>726</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="11">
         <f t="shared" si="3"/>
         <v>1316</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="11">
         <f t="shared" si="3"/>
         <v>531</v>
       </c>
-      <c r="O15" s="13">
+      <c r="O15" s="11">
         <f t="shared" si="3"/>
         <v>1101</v>
       </c>
-      <c r="P15" s="14">
+      <c r="P15" s="11">
         <f t="shared" si="3"/>
-        <v>1448</v>
-      </c>
-      <c r="Q15" s="14">
+        <v>900</v>
+      </c>
+      <c r="Q15" s="12">
         <f t="shared" si="3"/>
         <v>1108</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="15" t="s">
+    <row r="16" spans="1:25" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16">
         <f t="shared" ref="H16:Q16" si="4">H15/H13</f>
         <v>0.5715077605321508</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="16">
         <f t="shared" si="4"/>
         <v>0.5715077605321508</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="16">
         <f t="shared" si="4"/>
         <v>0.55964585274930101</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="16">
         <f t="shared" si="4"/>
         <v>0.73829321663019698</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="16">
         <f t="shared" si="4"/>
         <v>0.37154554759467756</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="16">
         <f t="shared" si="4"/>
         <v>0.81234567901234567</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="16">
         <f t="shared" si="4"/>
         <v>0.40909090909090912</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="16">
         <f t="shared" si="4"/>
         <v>0.74291497975708498</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="16">
         <f t="shared" si="4"/>
-        <v>0.57007874015748028</v>
-      </c>
-      <c r="Q16" s="19">
+        <v>0.5625</v>
+      </c>
+      <c r="Q16" s="17">
         <f t="shared" si="4"/>
         <v>0.56995884773662553</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="18">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="16">
         <f t="shared" ref="J17:Q17" si="5">J13/F13-1</f>
         <v>-4.0250447227191399E-2</v>
       </c>
-      <c r="K17" s="18">
+      <c r="K17" s="16">
         <f t="shared" si="5"/>
         <v>0.46099744245524299</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="16">
         <f t="shared" si="5"/>
         <v>8.314855875831495E-2</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="16">
         <f t="shared" si="5"/>
         <v>-0.10199556541019961</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N17" s="16">
         <f t="shared" si="5"/>
         <v>-0.39515377446411926</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="16">
         <f t="shared" si="5"/>
         <v>-0.35142231947483593</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="16">
         <f t="shared" si="5"/>
-        <v>0.29989764585465717</v>
-      </c>
-      <c r="Q17" s="19">
+        <v>-0.18116683725690885</v>
+      </c>
+      <c r="Q17" s="17">
         <f t="shared" si="5"/>
         <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
     </row>
     <row r="19" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
@@ -2674,214 +2785,214 @@
       <c r="O19" s="7">
         <v>9486</v>
       </c>
-      <c r="P19" s="8">
-        <v>11064</v>
+      <c r="P19" s="7">
+        <v>9200</v>
       </c>
       <c r="Q19" s="8">
         <v>10674</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11">
         <v>1502</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="11">
         <v>1502</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="11">
         <f>4343-K20</f>
         <v>1519</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="11">
         <v>2824</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="11">
         <v>4187</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="11">
         <f>13021-L20-K20-J20</f>
         <v>4491</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="11">
         <f>11144-O20</f>
         <v>5833</v>
       </c>
-      <c r="O20" s="13">
+      <c r="O20" s="11">
         <v>5311</v>
       </c>
-      <c r="P20" s="24">
-        <v>7413</v>
-      </c>
-      <c r="Q20" s="24">
+      <c r="P20" s="11">
+        <v>8000</v>
+      </c>
+      <c r="Q20" s="22">
         <v>7145</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11">
         <f t="shared" ref="H21:Q21" si="6">H19-H20</f>
         <v>152</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="11">
         <f t="shared" si="6"/>
         <v>152</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="11">
         <f t="shared" si="6"/>
         <v>604</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="11">
         <f t="shared" si="6"/>
         <v>2136</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="11">
         <f t="shared" si="6"/>
         <v>3443</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="11">
         <f t="shared" si="6"/>
         <v>3416</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="11">
         <f t="shared" si="6"/>
         <v>1651</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="11">
         <f t="shared" si="6"/>
         <v>4175</v>
       </c>
-      <c r="P21" s="25">
+      <c r="P21" s="11">
         <f t="shared" si="6"/>
-        <v>3651</v>
-      </c>
-      <c r="Q21" s="25">
+        <v>1200</v>
+      </c>
+      <c r="Q21" s="23">
         <f t="shared" si="6"/>
         <v>3529</v>
       </c>
     </row>
     <row r="22" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16">
         <f t="shared" ref="H22:Q22" si="7">H21/H19</f>
         <v>9.1898428053204348E-2</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="16">
         <f t="shared" si="7"/>
         <v>9.1898428053204348E-2</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="16">
         <f t="shared" si="7"/>
         <v>0.28450306170513423</v>
       </c>
-      <c r="K22" s="18">
+      <c r="K22" s="16">
         <f t="shared" si="7"/>
         <v>0.4306451612903226</v>
       </c>
-      <c r="L22" s="18">
+      <c r="L22" s="16">
         <f t="shared" si="7"/>
         <v>0.45124508519003931</v>
       </c>
-      <c r="M22" s="18">
+      <c r="M22" s="16">
         <f t="shared" si="7"/>
         <v>0.43202225875806249</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N22" s="16">
         <f t="shared" si="7"/>
         <v>0.22060395510422234</v>
       </c>
-      <c r="O22" s="18">
+      <c r="O22" s="16">
         <f t="shared" si="7"/>
         <v>0.4401222854733291</v>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="16">
         <f t="shared" si="7"/>
-        <v>0.32998915401301521</v>
-      </c>
-      <c r="Q22" s="19">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="Q22" s="17">
         <f t="shared" si="7"/>
         <v>0.33061645118980698</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="18">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="16">
         <f t="shared" ref="J23:Q23" si="8">J19/F19-1</f>
         <v>-0.18721286370597245</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="16">
         <f t="shared" si="8"/>
         <v>1.0840336134453783</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="16">
         <f t="shared" si="8"/>
         <v>3.6130592503022978</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="16">
         <f t="shared" si="8"/>
         <v>3.7805320435308341</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="16">
         <f t="shared" si="8"/>
         <v>2.5252001884126236</v>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="16">
         <f t="shared" si="8"/>
         <v>0.91250000000000009</v>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="16">
         <f t="shared" si="8"/>
-        <v>0.45006553079947564</v>
-      </c>
-      <c r="Q23" s="19">
+        <v>0.20576671035386629</v>
+      </c>
+      <c r="Q23" s="17">
         <f t="shared" si="8"/>
         <v>0.34994308840268107</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
     </row>
     <row r="25" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
@@ -2928,248 +3039,248 @@
         <f t="shared" si="9"/>
         <v>43970</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="7">
         <f t="shared" si="9"/>
-        <v>116427</v>
+        <v>41910</v>
       </c>
       <c r="Q25" s="8">
         <f t="shared" si="9"/>
-        <v>73364</v>
+        <v>42618</v>
       </c>
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11">
         <v>4888</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="11">
         <v>11315</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="11">
         <f t="shared" ref="H26:Q26" si="10">H8+H14+H20</f>
         <v>6050</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="11">
         <f t="shared" si="10"/>
         <v>6050</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="11">
         <f t="shared" si="10"/>
         <v>13179</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="11">
         <f t="shared" si="10"/>
         <v>7623</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="11">
         <f t="shared" si="10"/>
         <v>62181</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="11">
         <f t="shared" si="10"/>
         <v>42810</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="11">
         <f t="shared" si="10"/>
         <v>89749</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="11">
         <f t="shared" si="10"/>
         <v>36155</v>
       </c>
-      <c r="P26" s="14">
+      <c r="P26" s="11">
         <f t="shared" si="10"/>
-        <v>103405</v>
-      </c>
-      <c r="Q26" s="14">
+        <v>37200</v>
+      </c>
+      <c r="Q26" s="12">
         <f t="shared" si="10"/>
-        <v>64045</v>
+        <v>35481</v>
       </c>
     </row>
     <row r="27" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11">
         <f t="shared" ref="F27:Q27" si="11">F25-F26</f>
         <v>1686</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="11">
         <f t="shared" si="11"/>
         <v>3222</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="11">
         <f t="shared" si="11"/>
         <v>2830</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="11">
         <f t="shared" si="11"/>
         <v>2830</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="11">
         <f t="shared" si="11"/>
         <v>2714</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="11">
         <f t="shared" si="11"/>
         <v>4536</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="11">
         <f t="shared" si="11"/>
         <v>7887</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="11">
         <f t="shared" si="11"/>
         <v>7214</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="11">
         <f t="shared" si="11"/>
         <v>9210</v>
       </c>
-      <c r="O27" s="13">
+      <c r="O27" s="11">
         <f t="shared" si="11"/>
         <v>7815</v>
       </c>
-      <c r="P27" s="14">
+      <c r="P27" s="11">
         <f t="shared" si="11"/>
-        <v>13022</v>
-      </c>
-      <c r="Q27" s="14">
+        <v>4710</v>
+      </c>
+      <c r="Q27" s="12">
         <f t="shared" si="11"/>
-        <v>9319</v>
-      </c>
-      <c r="S27" s="23"/>
+        <v>7137</v>
+      </c>
+      <c r="S27" s="21"/>
     </row>
     <row r="28" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="18">
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="16">
         <f t="shared" ref="F28:Q28" si="12">F27/F25</f>
         <v>0.25646486157590509</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="16">
         <f t="shared" si="12"/>
         <v>0.22164132902249434</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="16">
         <f t="shared" si="12"/>
         <v>0.31869369369369371</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="16">
         <f t="shared" si="12"/>
         <v>0.31869369369369371</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="16">
         <f t="shared" si="12"/>
         <v>0.170767004341534</v>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="16">
         <f t="shared" si="12"/>
         <v>0.37305699481865284</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="16">
         <f t="shared" si="12"/>
         <v>0.11256208254838157</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="16">
         <f t="shared" si="12"/>
         <v>0.14421077882616345</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="16">
         <f t="shared" si="12"/>
         <v>9.3068846694085425E-2</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="16">
         <f t="shared" si="12"/>
         <v>0.17773481919490561</v>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="16">
         <f t="shared" si="12"/>
-        <v>0.11184690836318036</v>
-      </c>
-      <c r="Q28" s="19">
+        <v>0.11238367931281316</v>
+      </c>
+      <c r="Q28" s="17">
         <f t="shared" si="12"/>
-        <v>0.12702415353579413</v>
-      </c>
-      <c r="S28" s="23"/>
+        <v>0.16746445164015206</v>
+      </c>
+      <c r="S28" s="21"/>
     </row>
     <row r="29" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="P29" s="19">
+      <c r="P29" s="16">
         <f t="shared" ref="P29:Q29" si="13">P25/L25-1</f>
-        <v>0.66162870354512759</v>
-      </c>
-      <c r="Q29" s="19">
+        <v>-0.40186675800650795</v>
+      </c>
+      <c r="Q29" s="17">
         <f t="shared" si="13"/>
-        <v>0.46657604349912041</v>
+        <v>-0.14804893651047502</v>
       </c>
     </row>
     <row r="30" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
     </row>
     <row r="31" spans="2:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23">
+      <c r="E31" s="21"/>
+      <c r="F31" s="21">
         <v>2262</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="21">
         <v>2159</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="21">
         <v>2043</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="21">
         <v>2467</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="21">
         <v>2389</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="21">
         <v>2719</v>
       </c>
-      <c r="L31" s="23">
+      <c r="L31" s="21">
         <v>3885</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="21">
         <v>4247</v>
       </c>
-      <c r="N31" s="23">
+      <c r="N31" s="21">
         <v>4887</v>
       </c>
-      <c r="O31" s="23">
+      <c r="O31" s="21">
         <v>4735</v>
       </c>
-      <c r="P31" s="23">
+      <c r="P31" s="21">
         <v>6986</v>
       </c>
-      <c r="Q31" s="23">
+      <c r="Q31" s="21">
         <v>4769</v>
       </c>
     </row>
@@ -3177,241 +3288,241 @@
       <c r="B32" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23">
+      <c r="E32" s="21"/>
+      <c r="F32" s="21">
         <v>2351</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="21">
         <v>2247</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="21">
         <v>2115</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="21">
         <v>2538</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="21">
         <v>2461</v>
       </c>
-      <c r="K32" s="23">
+      <c r="K32" s="21">
         <v>2836</v>
       </c>
-      <c r="L32" s="23">
+      <c r="L32" s="21">
         <v>4093</v>
       </c>
-      <c r="M32" s="23">
+      <c r="M32" s="21">
         <v>4458</v>
       </c>
-      <c r="N32" s="23">
+      <c r="N32" s="21">
         <v>5097</v>
       </c>
-      <c r="O32" s="23">
+      <c r="O32" s="21">
         <v>5579</v>
       </c>
-      <c r="P32" s="23">
+      <c r="P32" s="21">
         <v>7568</v>
       </c>
-      <c r="Q32" s="23">
+      <c r="Q32" s="21">
         <v>5135</v>
       </c>
     </row>
-    <row r="33" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="29" t="s">
+    <row r="33" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23">
+      <c r="E33" s="21"/>
+      <c r="F33" s="21">
         <f t="shared" ref="F33:N33" si="14">F27-F32</f>
         <v>-665</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="21">
         <f t="shared" si="14"/>
         <v>975</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="21">
         <f t="shared" si="14"/>
         <v>715</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="21">
         <f t="shared" si="14"/>
         <v>292</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J33" s="21">
         <f t="shared" si="14"/>
         <v>253</v>
       </c>
-      <c r="K33" s="23">
+      <c r="K33" s="21">
         <f t="shared" si="14"/>
         <v>1700</v>
       </c>
-      <c r="L33" s="23">
+      <c r="L33" s="21">
         <f t="shared" si="14"/>
         <v>3794</v>
       </c>
-      <c r="M33" s="23">
+      <c r="M33" s="21">
         <f t="shared" si="14"/>
         <v>2756</v>
       </c>
-      <c r="N33" s="23">
+      <c r="N33" s="21">
         <f t="shared" si="14"/>
         <v>4113</v>
       </c>
-      <c r="O33" s="23">
+      <c r="O33" s="21">
         <f>O27-O32</f>
         <v>2236</v>
       </c>
-      <c r="P33" s="23">
+      <c r="P33" s="21">
         <f>P27-P32</f>
-        <v>5454</v>
-      </c>
-      <c r="Q33" s="23">
+        <v>-2858</v>
+      </c>
+      <c r="Q33" s="21">
         <f>Q27-Q32</f>
-        <v>4184</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="30" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="18">
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="16">
         <f t="shared" ref="F34:N34" si="15">F33/F25</f>
         <v>-0.10115606936416185</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="16">
         <f t="shared" si="15"/>
         <v>6.7070234573846046E-2</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="16">
         <f t="shared" si="15"/>
         <v>8.0518018018018014E-2</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="16">
         <f t="shared" si="15"/>
         <v>3.288288288288288E-2</v>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="16">
         <f t="shared" si="15"/>
         <v>1.5918958031837915E-2</v>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="16">
         <f t="shared" si="15"/>
         <v>0.13981412945143515</v>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="16">
         <f t="shared" si="15"/>
         <v>5.4147399668893079E-2</v>
       </c>
-      <c r="M34" s="18">
+      <c r="M34" s="16">
         <f t="shared" si="15"/>
         <v>5.5093555093555097E-2</v>
       </c>
-      <c r="N34" s="18">
+      <c r="N34" s="16">
         <f t="shared" si="15"/>
         <v>4.1562667367293527E-2</v>
       </c>
-      <c r="O34" s="18">
+      <c r="O34" s="16">
         <f>O33/O25</f>
         <v>5.0852854218785534E-2</v>
       </c>
-      <c r="P34" s="18">
+      <c r="P34" s="16">
         <f>P33/P25</f>
-        <v>4.6844804040299934E-2</v>
-      </c>
-      <c r="Q34" s="18">
+        <v>-6.8193748508709143E-2</v>
+      </c>
+      <c r="Q34" s="16">
         <f>Q33/Q25</f>
-        <v>5.7030696254293661E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="30" t="s">
+        <v>4.6975456379933361E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18">
+      <c r="E35" s="21"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16">
         <f t="shared" ref="K35:N35" si="16">K33/G33-1</f>
         <v>0.74358974358974361</v>
       </c>
-      <c r="L35" s="18">
+      <c r="L35" s="16">
         <f t="shared" si="16"/>
         <v>4.3062937062937063</v>
       </c>
-      <c r="M35" s="18">
+      <c r="M35" s="16">
         <f t="shared" si="16"/>
         <v>8.4383561643835616</v>
       </c>
-      <c r="N35" s="18">
+      <c r="N35" s="16">
         <f t="shared" si="16"/>
         <v>15.25691699604743</v>
       </c>
-      <c r="O35" s="18">
+      <c r="O35" s="16">
         <f>O33/K33-1</f>
         <v>0.31529411764705872</v>
       </c>
-      <c r="P35" s="18">
+      <c r="P35" s="16">
         <f>P33/L33-1</f>
-        <v>0.43753294675803911</v>
-      </c>
-      <c r="Q35" s="18">
+        <v>-1.7532946758039007</v>
+      </c>
+      <c r="Q35" s="16">
         <f>Q33/M33-1</f>
-        <v>0.5181422351233671</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-    </row>
-    <row r="37" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-0.27358490566037741</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+    </row>
+    <row r="37" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23">
+      <c r="E37" s="21"/>
+      <c r="F37" s="21">
         <v>89</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="21">
         <v>88</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="21">
         <v>95</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="21">
         <v>48</v>
       </c>
-      <c r="J37" s="23">
+      <c r="J37" s="21">
         <v>72</v>
       </c>
-      <c r="K37" s="23">
+      <c r="K37" s="21">
         <v>116</v>
       </c>
-      <c r="L37" s="23">
+      <c r="L37" s="21">
         <v>209</v>
       </c>
-      <c r="M37" s="23">
+      <c r="M37" s="21">
         <v>211</v>
       </c>
-      <c r="N37" s="23">
+      <c r="N37" s="21">
         <v>210</v>
       </c>
-      <c r="O37" s="23">
+      <c r="O37" s="21">
         <v>844</v>
       </c>
       <c r="P37" s="4">
@@ -3421,481 +3532,483 @@
         <v>890</v>
       </c>
     </row>
-    <row r="38" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="29" t="s">
+    <row r="38" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23">
+      <c r="E38" s="21"/>
+      <c r="F38" s="21">
         <f t="shared" ref="F38:N38" si="17">F33+F37</f>
         <v>-576</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="21">
         <f t="shared" si="17"/>
         <v>1063</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="21">
         <f t="shared" si="17"/>
         <v>810</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="21">
         <f t="shared" si="17"/>
         <v>340</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="21">
         <f t="shared" si="17"/>
         <v>325</v>
       </c>
-      <c r="K38" s="23">
+      <c r="K38" s="21">
         <f t="shared" si="17"/>
         <v>1816</v>
       </c>
-      <c r="L38" s="23">
+      <c r="L38" s="21">
         <f t="shared" si="17"/>
         <v>4003</v>
       </c>
-      <c r="M38" s="23">
+      <c r="M38" s="21">
         <f t="shared" si="17"/>
         <v>2967</v>
       </c>
-      <c r="N38" s="23">
+      <c r="N38" s="21">
         <f t="shared" si="17"/>
         <v>4323</v>
       </c>
-      <c r="O38" s="23">
+      <c r="O38" s="21">
         <f>O33+O37</f>
         <v>3080</v>
       </c>
-      <c r="P38" s="23">
+      <c r="P38" s="21">
         <f>P33+P37</f>
-        <v>6284</v>
-      </c>
-      <c r="Q38" s="23">
+        <v>-2028</v>
+      </c>
+      <c r="Q38" s="21">
         <f>Q33+Q37</f>
-        <v>5074</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-    </row>
-    <row r="40" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2892</v>
+      </c>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+    </row>
+    <row r="39" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21"/>
+    </row>
+    <row r="40" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23">
+      <c r="E40" s="21"/>
+      <c r="F40" s="21">
         <v>-112</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="21">
         <v>648</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="21">
         <v>-481</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="21">
         <v>-729</v>
       </c>
-      <c r="J40" s="23">
+      <c r="J40" s="21">
         <v>-328</v>
       </c>
-      <c r="K40" s="23">
+      <c r="K40" s="21">
         <v>-378</v>
       </c>
-      <c r="L40" s="23">
+      <c r="L40" s="21">
         <v>-1128</v>
       </c>
-      <c r="M40" s="23">
+      <c r="M40" s="21">
         <v>-1109</v>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="21">
         <v>-1468</v>
       </c>
-      <c r="O40" s="23">
+      <c r="O40" s="21">
         <v>-859</v>
       </c>
-      <c r="P40" s="23">
+      <c r="P40" s="21">
         <v>-850</v>
       </c>
-      <c r="Q40" s="23">
+      <c r="Q40" s="21">
         <v>-800</v>
       </c>
     </row>
-    <row r="41" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="21">
         <v>0</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="21">
         <v>0</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="21">
         <v>0</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="21">
         <v>355</v>
       </c>
-      <c r="J41" s="23">
+      <c r="J41" s="21">
         <v>100</v>
       </c>
-      <c r="K41" s="23">
+      <c r="K41" s="21">
         <v>106</v>
       </c>
-      <c r="L41" s="23">
+      <c r="L41" s="21">
         <v>0</v>
       </c>
-      <c r="M41" s="23">
+      <c r="M41" s="21">
         <v>562</v>
       </c>
-      <c r="N41" s="23">
+      <c r="N41" s="21">
         <v>383</v>
       </c>
-      <c r="O41" s="23">
+      <c r="O41" s="21">
         <v>175</v>
       </c>
-      <c r="P41" s="23">
+      <c r="P41" s="21">
         <v>200</v>
       </c>
-      <c r="Q41" s="23">
+      <c r="Q41" s="21">
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="29" t="s">
+    <row r="42" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23">
+      <c r="E42" s="21"/>
+      <c r="F42" s="21">
         <f t="shared" ref="F42:N42" si="18">F33+F40+F41</f>
         <v>-777</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="21">
         <f t="shared" si="18"/>
         <v>1623</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="21">
         <f t="shared" si="18"/>
         <v>234</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="21">
         <f t="shared" si="18"/>
         <v>-82</v>
       </c>
-      <c r="J42" s="23">
+      <c r="J42" s="21">
         <f t="shared" si="18"/>
         <v>25</v>
       </c>
-      <c r="K42" s="23">
+      <c r="K42" s="21">
         <f t="shared" si="18"/>
         <v>1428</v>
       </c>
-      <c r="L42" s="23">
+      <c r="L42" s="21">
         <f t="shared" si="18"/>
         <v>2666</v>
       </c>
-      <c r="M42" s="23">
+      <c r="M42" s="21">
         <f t="shared" si="18"/>
         <v>2209</v>
       </c>
-      <c r="N42" s="23">
+      <c r="N42" s="21">
         <f t="shared" si="18"/>
         <v>3028</v>
       </c>
-      <c r="O42" s="23">
+      <c r="O42" s="21">
         <f>O33+O40+O41</f>
         <v>1552</v>
       </c>
-      <c r="P42" s="23">
+      <c r="P42" s="21">
         <f>P33+P40+P41</f>
-        <v>4804</v>
-      </c>
-      <c r="Q42" s="23">
+        <v>-3508</v>
+      </c>
+      <c r="Q42" s="21">
         <f>Q33+Q40+Q41</f>
-        <v>3564</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-    </row>
-    <row r="44" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+    </row>
+    <row r="44" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="21">
         <v>9</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="21">
         <v>12</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="21">
         <v>24</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="21">
         <v>15</v>
       </c>
-      <c r="J44" s="23">
+      <c r="J44" s="21">
         <v>10</v>
       </c>
-      <c r="K44" s="23">
+      <c r="K44" s="21">
         <v>26</v>
       </c>
-      <c r="L44" s="23">
+      <c r="L44" s="21">
         <v>20</v>
       </c>
-      <c r="M44" s="23">
+      <c r="M44" s="21">
         <v>102</v>
       </c>
-      <c r="N44" s="23">
+      <c r="N44" s="21">
         <v>49</v>
       </c>
-      <c r="O44" s="23">
+      <c r="O44" s="21">
         <v>69</v>
       </c>
-      <c r="P44" s="23">
+      <c r="P44" s="21">
         <v>225</v>
       </c>
-      <c r="Q44" s="23">
+      <c r="Q44" s="21">
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="16">
         <v>0</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="16">
         <f t="shared" ref="G45:N45" si="19">G44/G42</f>
         <v>7.3937153419593345E-3</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="16">
         <f t="shared" si="19"/>
         <v>0.10256410256410256</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="16">
         <f t="shared" si="19"/>
         <v>-0.18292682926829268</v>
       </c>
-      <c r="J45" s="18">
+      <c r="J45" s="16">
         <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
-      <c r="K45" s="18">
+      <c r="K45" s="16">
         <f t="shared" si="19"/>
         <v>1.8207282913165267E-2</v>
       </c>
-      <c r="L45" s="18">
+      <c r="L45" s="16">
         <f t="shared" si="19"/>
         <v>7.5018754688672166E-3</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M45" s="16">
         <f t="shared" si="19"/>
         <v>4.6174739701222274E-2</v>
       </c>
-      <c r="N45" s="18">
+      <c r="N45" s="16">
         <f t="shared" si="19"/>
         <v>1.6182298546895641E-2</v>
       </c>
-      <c r="O45" s="18">
+      <c r="O45" s="16">
         <f>O44/O42</f>
         <v>4.445876288659794E-2</v>
       </c>
-      <c r="P45" s="18">
+      <c r="P45" s="16">
         <f>P44/P42</f>
-        <v>4.6835970024979183E-2</v>
-      </c>
-      <c r="Q45" s="18">
+        <v>-6.4139110604332958E-2</v>
+      </c>
+      <c r="Q45" s="16">
         <f>Q44/Q42</f>
-        <v>4.4893378226711557E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="23"/>
-    </row>
-    <row r="47" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="29" t="s">
+        <v>0.11577424023154848</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="21"/>
+    </row>
+    <row r="47" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="21">
         <f t="shared" ref="F47:N47" si="20">F42-F44</f>
         <v>-786</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="21">
         <f t="shared" si="20"/>
         <v>1611</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="21">
         <f t="shared" si="20"/>
         <v>210</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="21">
         <f t="shared" si="20"/>
         <v>-97</v>
       </c>
-      <c r="J47" s="23">
+      <c r="J47" s="21">
         <f t="shared" si="20"/>
         <v>15</v>
       </c>
-      <c r="K47" s="23">
+      <c r="K47" s="21">
         <f t="shared" si="20"/>
         <v>1402</v>
       </c>
-      <c r="L47" s="23">
+      <c r="L47" s="21">
         <f t="shared" si="20"/>
         <v>2646</v>
       </c>
-      <c r="M47" s="23">
+      <c r="M47" s="21">
         <f t="shared" si="20"/>
         <v>2107</v>
       </c>
-      <c r="N47" s="23">
+      <c r="N47" s="21">
         <f t="shared" si="20"/>
         <v>2979</v>
       </c>
-      <c r="O47" s="23">
+      <c r="O47" s="21">
         <f>O42-O44</f>
         <v>1483</v>
       </c>
-      <c r="P47" s="23">
+      <c r="P47" s="21">
         <f>P42-P44</f>
-        <v>4579</v>
-      </c>
-      <c r="Q47" s="23">
+        <v>-3733</v>
+      </c>
+      <c r="Q47" s="21">
         <f>Q42-Q44</f>
-        <v>3404</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="15" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="34">
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="32">
         <f>-(47/F47-1)</f>
         <v>1.059796437659033</v>
       </c>
-      <c r="K48" s="34">
+      <c r="K48" s="32">
         <f t="shared" ref="K48:N48" si="21">K47/G47-1</f>
         <v>-0.12973308504034764</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="32">
         <f t="shared" si="21"/>
         <v>11.6</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="32">
         <f>-(M47/I47-1)</f>
         <v>22.721649484536083</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="32">
         <f t="shared" si="21"/>
         <v>197.6</v>
       </c>
-      <c r="O48" s="18">
+      <c r="O48" s="16">
         <f>O47/K47-1</f>
         <v>5.7774607703281022E-2</v>
       </c>
-      <c r="P48" s="18">
+      <c r="P48" s="16">
         <f>P47/L47-1</f>
-        <v>0.73053665910808774</v>
-      </c>
-      <c r="Q48" s="18">
+        <v>-2.4108087679516252</v>
+      </c>
+      <c r="Q48" s="16">
         <f>Q47/M47-1</f>
-        <v>0.61556715709539622</v>
+        <v>-0.4200284765068818</v>
       </c>
     </row>
     <row r="49" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="21"/>
     </row>
     <row r="50" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F50" s="23">
+      <c r="F50" s="21">
         <v>-13730</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="21">
         <v>17515</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="21">
         <v>4554</v>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="21">
         <v>-16865</v>
       </c>
-      <c r="J50" s="23">
+      <c r="J50" s="21">
         <v>2607</v>
       </c>
-      <c r="K50" s="23">
+      <c r="K50" s="21">
         <v>-6010</v>
       </c>
-      <c r="L50" s="23">
+      <c r="L50" s="21">
         <v>38582</v>
       </c>
-      <c r="M50" s="23">
+      <c r="M50" s="21">
         <v>-28366</v>
       </c>
-      <c r="N50" s="23">
+      <c r="N50" s="21">
         <v>5764</v>
       </c>
-      <c r="O50" s="23">
+      <c r="O50" s="21">
         <v>5430</v>
       </c>
-      <c r="P50" s="23">
+      <c r="P50" s="21">
         <v>-1591</v>
       </c>
-      <c r="Q50" s="23">
+      <c r="Q50" s="21">
         <v>-46</v>
       </c>
     </row>
@@ -3903,18 +4016,18 @@
       <c r="B51" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
     </row>
     <row r="55" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="S55" s="4"/>
@@ -3967,16 +4080,16 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32"/>
-      <c r="T60" s="32"/>
-      <c r="U60" s="32"/>
-      <c r="V60" s="32"/>
-      <c r="W60" s="32"/>
-      <c r="X60" s="32"/>
-      <c r="Y60" s="32"/>
-      <c r="Z60" s="32"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
+      <c r="X60" s="30"/>
+      <c r="Y60" s="30"/>
+      <c r="Z60" s="30"/>
     </row>
     <row r="61" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="S61" s="4"/>
@@ -4009,16 +4122,16 @@
       <c r="Z63" s="4"/>
     </row>
     <row r="64" spans="2:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q64" s="33"/>
-      <c r="R64" s="33"/>
-      <c r="S64" s="33"/>
-      <c r="T64" s="33"/>
-      <c r="U64" s="33"/>
-      <c r="V64" s="33"/>
-      <c r="W64" s="33"/>
-      <c r="X64" s="33"/>
-      <c r="Y64" s="33"/>
-      <c r="Z64" s="33"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="31"/>
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
     </row>
     <row r="65" spans="17:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="S65" s="4"/>
@@ -4111,16 +4224,16 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" spans="17:26" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q74" s="33"/>
-      <c r="R74" s="33"/>
-      <c r="S74" s="33"/>
-      <c r="T74" s="33"/>
-      <c r="U74" s="33"/>
-      <c r="V74" s="33"/>
-      <c r="W74" s="33"/>
-      <c r="X74" s="33"/>
-      <c r="Y74" s="33"/>
-      <c r="Z74" s="33"/>
+      <c r="Q74" s="31"/>
+      <c r="R74" s="31"/>
+      <c r="S74" s="31"/>
+      <c r="T74" s="31"/>
+      <c r="U74" s="31"/>
+      <c r="V74" s="31"/>
+      <c r="W74" s="31"/>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
